--- a/services/integrator/internal/document/testdata/kartu-stok-sebelum-buku.golden.xlsx
+++ b/services/integrator/internal/document/testdata/kartu-stok-sebelum-buku.golden.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Catatan: 14 barang tanpa saldo awal dan tanpa mutasi tidak ditampilkan.</t>
+    <t xml:space="preserve">Catatan: 15 barang tanpa saldo awal dan tanpa mutasi tidak ditampilkan.</t>
   </si>
 </sst>
 </file>
